--- a/workspace/Health Facility Data/UtahHealth24_xlsx.xlsx
+++ b/workspace/Health Facility Data/UtahHealth24_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c1929351461b30c/Documents/internship/workspace/Health Facility Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{5CA8E062-45E9-4EC9-A8DC-BBEF1B3BE706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C538AC2E-17E8-4277-BA1A-89C1308779DF}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{5CA8E062-45E9-4EC9-A8DC-BBEF1B3BE706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89FDFC12-8AB1-4CBB-8164-739FD087E77B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{F893E8D5-7F3E-4353-8353-B858F28181E1}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6151" uniqueCount="2596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6148" uniqueCount="2596">
   <si>
     <t>state</t>
   </si>
@@ -8352,6 +8352,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -35933,7 +35937,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A54BD73-93E9-4915-AFF0-423E7620A337}">
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -35941,16 +35945,13 @@
     <col min="8" max="8" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -35982,25 +35983,16 @@
         <v>17</v>
       </c>
       <c r="K1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -36032,25 +36024,16 @@
         <v>14</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M2">
-        <v>35</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -36085,22 +36068,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M3">
-        <v>17</v>
-      </c>
-      <c r="N3">
-        <v>3</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -36135,22 +36109,13 @@
         <v>0</v>
       </c>
       <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -36182,25 +36147,16 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>7</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -36235,22 +36191,13 @@
         <v>0</v>
       </c>
       <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -36282,25 +36229,16 @@
         <v>2</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>4</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -36335,22 +36273,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>8</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -36382,25 +36311,16 @@
         <v>8</v>
       </c>
       <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>11</v>
+      </c>
+      <c r="M9">
         <v>1</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>11</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -36435,22 +36355,13 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -36490,17 +36401,8 @@
       <c r="M11">
         <v>0</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -36532,25 +36434,16 @@
         <v>0</v>
       </c>
       <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>3</v>
+      </c>
+      <c r="M12">
         <v>1</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>3</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -36585,22 +36478,13 @@
         <v>0</v>
       </c>
       <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
-      <c r="M13">
-        <v>2</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -36635,22 +36519,13 @@
         <v>0</v>
       </c>
       <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
         <v>0</v>
       </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -36685,22 +36560,13 @@
         <v>0</v>
       </c>
       <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
         <v>0</v>
       </c>
-      <c r="M15">
-        <v>2</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -36735,22 +36601,13 @@
         <v>0</v>
       </c>
       <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
         <v>0</v>
       </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -36785,22 +36642,13 @@
         <v>0</v>
       </c>
       <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
         <v>0</v>
       </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -36838,19 +36686,10 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -36888,19 +36727,10 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -36935,22 +36765,13 @@
         <v>0</v>
       </c>
       <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
         <v>0</v>
       </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -36985,22 +36806,13 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21">
         <v>1</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -37035,22 +36847,13 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -37085,22 +36888,13 @@
         <v>0</v>
       </c>
       <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
         <v>0</v>
       </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -37140,17 +36934,8 @@
       <c r="M24">
         <v>0</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -37185,22 +36970,13 @@
         <v>0</v>
       </c>
       <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -37235,18 +37011,9 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
         <v>1</v>
       </c>
     </row>
